--- a/src/assets/projets/Projet_habibo_storek.xlsx
+++ b/src/assets/projets/Projet_habibo_storek.xlsx
@@ -41,8 +41,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -551,20 +555,151 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>phase</v>
+      </c>
+      <c r="B1" t="str">
+        <v>dateDebut</v>
+      </c>
+      <c r="C1" t="str">
+        <v>dateFin</v>
+      </c>
+      <c r="D1" t="str">
+        <v>dateFinReelle</v>
+      </c>
+      <c r="E1" t="str">
+        <v>nombreJours</v>
+      </c>
+      <c r="F1" t="str">
+        <v>pourcentageRealisation</v>
+      </c>
+      <c r="G1" t="str">
+        <v>avanceRetard</v>
+      </c>
+      <c r="H1" t="str">
+        <v>etat</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Phase 1 – Vérification du câblage et test hydraulique</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>-80</v>
+      </c>
+      <c r="H2" t="str">
+        <v>EN_RETARD</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Phase 2 – Développement et tests</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>-66</v>
+      </c>
+      <c r="H3" t="str">
+        <v>EN_RETARD</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Phase 3 – Test à l’eau et test en charge</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>-10</v>
+      </c>
+      <c r="H4" t="str">
+        <v>EN_RETARD</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Phase 4 – Commissioning / Mise en service sur le lait</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="str">
+        <v>A_VENIR</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetData/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
-  </ignoredErrors>
-</worksheet>
 </file>